--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488058_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488058_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7061</v>
+        <v>8.654299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4721</v>
+        <v>6.0833</v>
       </c>
       <c r="F2" t="n">
-        <v>2.234</v>
+        <v>2.571</v>
       </c>
       <c r="G2" t="n">
         <v>6.1944</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0374</v>
+        <v>0.9856</v>
       </c>
       <c r="T2" t="n">
-        <v>0.18</v>
+        <v>0.7912</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1425</v>
+        <v>0.1944</v>
       </c>
       <c r="V2" t="n">
         <v>-0.508</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7014</v>
+        <v>4.6276</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4493</v>
+        <v>3.3475</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2521</v>
+        <v>1.2802</v>
       </c>
       <c r="G3" t="n">
         <v>1.7437</v>
@@ -688,13 +688,13 @@
         <v>1.3876</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2081</v>
+        <v>1.1343</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7967</v>
+        <v>0.6948</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4114</v>
+        <v>0.4395</v>
       </c>
       <c r="V3" t="n">
         <v>0.3621</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2617</v>
+        <v>3.8462</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8363</v>
+        <v>4.201</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4254</v>
+        <v>-0.3548</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3404</v>
+        <v>-0.6279</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2322</v>
+        <v>2.0946</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5726</v>
+        <v>-2.7225</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7243</v>
+        <v>3.0929</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2294</v>
+        <v>2.4824</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4949</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3839</v>
+        <v>-3.7208</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4617</v>
+        <v>-0.3879</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9223</v>
+        <v>-3.3329</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.5769</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>-0.1982</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9822</v>
+        <v>2.7751</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9213</v>
+        <v>0.6902</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.0993</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3008</v>
+        <v>0.5909</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4737</v>
+        <v>1.2071</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0269</v>
+        <v>3.0915</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6064</v>
+        <v>1.9545</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5794</v>
+        <v>1.1371</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6279</v>
+        <v>0.8036</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0946</v>
+        <v>0.222</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.7225</v>
+        <v>0.5817</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0929</v>
+        <v>3.5886</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4824</v>
+        <v>1.6886</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6104000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.7208</v>
+        <v>-2.785</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3879</v>
+        <v>-1.4666</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.3329</v>
+        <v>-1.3184</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5769</v>
+        <v>1.5858</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7751</v>
+        <v>3.7662</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1291</v>
+        <v>1.3509</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4954</v>
+        <v>0.9537</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3662</v>
+        <v>0.3972</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2071</v>
+        <v>-0.6488</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2071</v>
+        <v>-0.4074</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2414</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7182</v>
+        <v>2.7275</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6654</v>
+        <v>0.4198</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0528</v>
+        <v>2.3078</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8036</v>
+        <v>1.5176</v>
       </c>
       <c r="H7" t="n">
-        <v>0.222</v>
+        <v>2.1413</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5817</v>
+        <v>-0.6237</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5886</v>
+        <v>0.2025</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6886</v>
+        <v>0.7131</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.785</v>
+        <v>1.3151</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4666</v>
+        <v>1.4281</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3184</v>
+        <v>-0.113</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5858</v>
+        <v>0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>3.7662</v>
+        <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9776</v>
+        <v>1.0801</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6647</v>
+        <v>0.6048</v>
       </c>
       <c r="U7" t="n">
-        <v>0.313</v>
+        <v>0.4752</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6488</v>
+        <v>-0.2666</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.4074</v>
+        <v>0.6036</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2414</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.557</v>
+        <v>2.694</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1931</v>
+        <v>2.7179</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3639</v>
+        <v>-0.0239</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5176</v>
+        <v>1.3404</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1413</v>
+        <v>-0.2322</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6237</v>
+        <v>1.5726</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2025</v>
+        <v>2.7243</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7131</v>
+        <v>0.2294</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5106000000000001</v>
+        <v>2.4949</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3151</v>
+        <v>-1.3839</v>
       </c>
       <c r="N8" t="n">
-        <v>1.4281</v>
+        <v>-0.4617</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.113</v>
+        <v>-0.9223</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9096</v>
+        <v>1.3536</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3782</v>
+        <v>0.5021</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5314</v>
+        <v>0.8515</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6036</v>
+        <v>1.4737</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8701</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.1082</v>
+        <v>2.6333</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0333</v>
+        <v>1.3618</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0749</v>
+        <v>1.2715</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8814</v>
@@ -1156,13 +1156,13 @@
         <v>2.7751</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3</v>
+        <v>0.825</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1834</v>
+        <v>0.1451</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4834</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>3.8879</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8414</v>
+        <v>1.8134</v>
       </c>
       <c r="E10" t="n">
         <v>0.9903999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.851</v>
+        <v>0.8229</v>
       </c>
       <c r="G10" t="n">
         <v>0.4866</v>
@@ -1234,13 +1234,13 @@
         <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2954</v>
+        <v>1.2673</v>
       </c>
       <c r="T10" t="n">
         <v>0.9215</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3739</v>
+        <v>0.3459</v>
       </c>
       <c r="V10" t="n">
         <v>-0.337</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2662</v>
+        <v>0.8859</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06569999999999999</v>
+        <v>-0.4832</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2005</v>
+        <v>1.369</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5002</v>
@@ -1312,13 +1312,13 @@
         <v>2.7751</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1807</v>
+        <v>0.8003</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1638</v>
+        <v>0.615</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0168</v>
+        <v>0.1853</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4264</v>
+        <v>-1.7716</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6814</v>
+        <v>-0.4392</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1078</v>
+        <v>-1.3324</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5914</v>
@@ -1468,13 +1468,13 @@
         <v>1.3876</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7612</v>
+        <v>1.416</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0302</v>
+        <v>0.9096</v>
       </c>
       <c r="U13" t="n">
-        <v>0.731</v>
+        <v>0.5064</v>
       </c>
       <c r="V13" t="n">
         <v>-2.9926</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. JIMENEZ EXPOSITO</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.3501</v>
+        <v>-3.1883</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.8302</v>
+        <v>-2.5146</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5199</v>
+        <v>-0.6737</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.0034</v>
+        <v>-3.1239</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5207000000000001</v>
+        <v>1.3853</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4827</v>
+        <v>-4.5092</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5984</v>
+        <v>-0.3949</v>
       </c>
       <c r="K14" t="n">
-        <v>0.08069999999999999</v>
+        <v>1.036</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6791</v>
+        <v>-1.4308</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.405</v>
+        <v>-2.729</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6014</v>
+        <v>0.3494</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8036</v>
+        <v>-3.0784</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5858</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9822</v>
+        <v>-2.1805</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3964</v>
+        <v>1.5858</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4805</v>
+        <v>0.4598</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2496</v>
+        <v>0.0607</v>
       </c>
       <c r="U14" t="n">
-        <v>0.73</v>
+        <v>0.3991</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2414</v>
+        <v>0.0704</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2414</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>D. JIMENEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.89</v>
+        <v>-3.5571</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.1883</v>
+        <v>-2.7284</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7018</v>
+        <v>-0.8288</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.1239</v>
+        <v>-2.0034</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3853</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.5092</v>
+        <v>-1.4827</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3949</v>
+        <v>-0.5984</v>
       </c>
       <c r="K15" t="n">
-        <v>1.036</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4308</v>
+        <v>-0.6791</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.729</v>
+        <v>-1.405</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3494</v>
+        <v>-0.6014</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.0784</v>
+        <v>-0.8036</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5947</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1805</v>
+        <v>-1.9822</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5858</v>
+        <v>0.3964</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2419</v>
+        <v>0.2735</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6129</v>
+        <v>-0.1477</v>
       </c>
       <c r="U15" t="n">
-        <v>0.371</v>
+        <v>0.4212</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0704</v>
+        <v>-0.2414</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0704</v>
+        <v>-0.2414</v>
       </c>
     </row>
     <row r="16">
@@ -1657,16 +1657,16 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>25.1393</v>
+        <v>26.0754</v>
       </c>
       <c r="E16" t="n">
-        <v>17.5936</v>
+        <v>18.5295</v>
       </c>
       <c r="F16" t="n">
-        <v>7.545700000000002</v>
+        <v>7.5459</v>
       </c>
       <c r="G16" t="n">
-        <v>5.9768</v>
+        <v>5.976800000000001</v>
       </c>
       <c r="H16" t="n">
         <v>7.392</v>
@@ -1678,7 +1678,7 @@
         <v>20.0693</v>
       </c>
       <c r="K16" t="n">
-        <v>8.243699999999999</v>
+        <v>8.2437</v>
       </c>
       <c r="L16" t="n">
         <v>11.8254</v>
@@ -1693,7 +1693,7 @@
         <v>-13.2406</v>
       </c>
       <c r="P16" t="n">
-        <v>7.928800000000001</v>
+        <v>7.928800000000002</v>
       </c>
       <c r="Q16" t="n">
         <v>-15.8577</v>
@@ -1702,19 +1702,19 @@
         <v>23.7867</v>
       </c>
       <c r="S16" t="n">
-        <v>10.7008</v>
+        <v>11.6366</v>
       </c>
       <c r="T16" t="n">
-        <v>5.2143</v>
+        <v>6.150099999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>5.4864</v>
+        <v>5.486499999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5330999999999995</v>
+        <v>0.5331000000000004</v>
       </c>
       <c r="W16" t="n">
-        <v>8.168200000000002</v>
+        <v>8.168200000000001</v>
       </c>
       <c r="X16" t="n">
         <v>-7.634899999999999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>8.8573</v>
+        <v>9.910600000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>8.490399999999999</v>
+        <v>8.8979</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3669</v>
+        <v>1.0127</v>
       </c>
       <c r="G17" t="n">
         <v>11.5585</v>
@@ -1780,13 +1780,13 @@
         <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.9261</v>
+        <v>-0.8728</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.5174</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0011</v>
+        <v>-0.3553</v>
       </c>
       <c r="V17" t="n">
         <v>1.2071</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.7439</v>
+        <v>4.5441</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1208</v>
+        <v>3.4265</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6231</v>
+        <v>1.1176</v>
       </c>
       <c r="G18" t="n">
         <v>5.4956</v>
@@ -1858,13 +1858,13 @@
         <v>1.9822</v>
       </c>
       <c r="S18" t="n">
-        <v>0.074</v>
+        <v>-0.1258</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.6193</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9989</v>
+        <v>0.4935</v>
       </c>
       <c r="V18" t="n">
         <v>2.1476</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0397</v>
+        <v>0.8713</v>
       </c>
       <c r="E19" t="n">
         <v>0.0026</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0372</v>
+        <v>0.8687</v>
       </c>
       <c r="G19" t="n">
         <v>0.3804</v>
@@ -1936,13 +1936,13 @@
         <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1262</v>
+        <v>-0.0422</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2496</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3758</v>
+        <v>0.2074</v>
       </c>
       <c r="V19" t="n">
         <v>0.5331</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0282</v>
+        <v>-1.498</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6113</v>
+        <v>-0.3057</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4169</v>
+        <v>-1.1923</v>
       </c>
       <c r="G21" t="n">
         <v>0.6259</v>
@@ -2092,13 +2092,13 @@
         <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.4382</v>
+        <v>-1.9079</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8112</v>
+        <v>-0.5056</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.627</v>
+        <v>-1.4024</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2071</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8076</v>
+        <v>-2.9199</v>
       </c>
       <c r="E22" t="n">
         <v>-1.2689</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5387</v>
+        <v>-1.651</v>
       </c>
       <c r="G22" t="n">
         <v>0.1031</v>
@@ -2170,13 +2170,13 @@
         <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.765</v>
+        <v>-0.8774</v>
       </c>
       <c r="T22" t="n">
         <v>-0.4992</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2659</v>
+        <v>-0.3782</v>
       </c>
       <c r="V22" t="n">
         <v>-2.3438</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4693</v>
+        <v>-4.1369</v>
       </c>
       <c r="E23" t="n">
         <v>-1.2818</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1875</v>
+        <v>-2.8551</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5778</v>
@@ -2248,13 +2248,13 @@
         <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8915</v>
+        <v>-1.5592</v>
       </c>
       <c r="T23" t="n">
         <v>-0.6936</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1979</v>
+        <v>-0.8655</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6036</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0084</v>
+        <v>-4.8693</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2053</v>
+        <v>-1.5109</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8031</v>
+        <v>-3.3584</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0691</v>
@@ -2326,13 +2326,13 @@
         <v>1.784</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.534</v>
+        <v>-1.3949</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3778</v>
+        <v>-0.6834</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1561</v>
+        <v>-0.7114</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2071</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.4489</v>
+        <v>-8.457800000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3798</v>
+        <v>-3.991</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.0691</v>
+        <v>-4.4668</v>
       </c>
       <c r="G25" t="n">
         <v>-5.9875</v>
@@ -2404,13 +2404,13 @@
         <v>1.1893</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9767</v>
+        <v>-0.0321</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3085</v>
+        <v>-0.3027</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6682</v>
+        <v>0.2705</v>
       </c>
       <c r="V25" t="n">
         <v>0.337</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBINO</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.9955</v>
+        <v>-9.099500000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.3108</v>
+        <v>-5.3988</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.6847</v>
+        <v>-3.7007</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.576700000000001</v>
+        <v>-6.5318</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.8544</v>
+        <v>-3.7176</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.7223</v>
+        <v>-2.8142</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.7415</v>
+        <v>-2.8656</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.6673</v>
+        <v>-2.7165</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.0742</v>
+        <v>-0.149</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.8352</v>
+        <v>-3.6662</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.1871</v>
+        <v>-1.001</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.6481</v>
+        <v>-2.6652</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R26" t="n">
-        <v>1.9822</v>
+        <v>1.1893</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0223</v>
+        <v>-1.7748</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1906</v>
+        <v>-0.8175</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8317</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.6036</v>
+        <v>0.2666</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>A. CONTRERAS RUBINO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.6252</v>
+        <v>-9.407500000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.7044</v>
+        <v>-6.7183</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.9208</v>
+        <v>-2.6892</v>
       </c>
       <c r="G27" t="n">
-        <v>-6.5318</v>
+        <v>-8.576700000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.7176</v>
+        <v>-2.8544</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.8142</v>
+        <v>-5.7223</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.8656</v>
+        <v>-4.7415</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.7165</v>
+        <v>-1.6673</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.149</v>
+        <v>-3.0742</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.6662</v>
+        <v>-3.8352</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.001</v>
+        <v>-1.1871</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.6652</v>
+        <v>-2.6481</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R27" t="n">
-        <v>1.1893</v>
+        <v>1.9822</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.3005</v>
+        <v>-1.4344</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.1232</v>
+        <v>-0.5981</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.1773</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W27" t="n">
-        <v>0.2666</v>
+        <v>0.6036</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-25.1395</v>
+        <v>-24.4602</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.5458</v>
+        <v>-7.545699999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-17.5936</v>
+        <v>-16.9145</v>
       </c>
       <c r="G28" t="n">
         <v>-5.976700000000002</v>
@@ -2638,13 +2638,13 @@
         <v>15.8576</v>
       </c>
       <c r="S28" t="n">
-        <v>-10.7007</v>
+        <v>-10.0215</v>
       </c>
       <c r="T28" t="n">
-        <v>-5.4865</v>
+        <v>-5.4864</v>
       </c>
       <c r="U28" t="n">
-        <v>-5.2141</v>
+        <v>-4.5348</v>
       </c>
       <c r="V28" t="n">
         <v>-0.5331999999999998</v>
